--- a/flasheo/logs/registro_flasheo.xlsx
+++ b/flasheo/logs/registro_flasheo.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I485"/>
+  <dimension ref="A1:I652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17953,9 +17953,6 @@
           <t>192.168.1.1</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr">
         <is>
           <t>ERROR</t>
@@ -17969,6 +17966,6629 @@
       <c r="I485" t="inlineStr">
         <is>
           <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="n">
+        <v>46289.7940625</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>192.168.1.1</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="n">
+        <v>46289.81855324074</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>192.168.1.1</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="n">
+        <v>46289.91890046297</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="n">
+        <v>46289.92215277778</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="n">
+        <v>46289.92538194444</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="n">
+        <v>46289.93127314815</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="n">
+        <v>46289.93451388889</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="n">
+        <v>46289.93774305555</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="n">
+        <v>46289.94362268518</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="n">
+        <v>46289.94686342592</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="n">
+        <v>46289.95010416667</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="n">
+        <v>46289.9559837963</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="n">
+        <v>46289.95922453704</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="n">
+        <v>46289.96246527778</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="n">
+        <v>46289.96834490741</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="n">
+        <v>46289.97158564815</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46289.97482638889</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46289.9807175926</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="n">
+        <v>46289.98395833333</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="n">
+        <v>46289.98719907407</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="n">
+        <v>46289.99310185185</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="n">
+        <v>46289.99635416667</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>46289.99959490741</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>46290.00546296296</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>46290.0087037037</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
+        <v>46290.01194444444</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>46290.01782407407</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>46290.02106481481</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>46290.02430555555</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>46290.03021990741</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>46290.03346064815</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>46290.03670138889</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>46290.04261574074</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>46290.04585648148</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>46290.04909722223</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>46290.055</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>46290.05824074074</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>46290.06148148148</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="n">
+        <v>46290.06736111111</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="n">
+        <v>46290.07061342592</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>46290.07385416667</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>46290.07973379629</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>46290.08297453704</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>46290.08621527778</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>46290.09210648148</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>46290.09533564815</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>46290.09858796297</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>46290.1044675926</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>46290.10771990741</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>46290.11097222222</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>46290.11685185185</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>46290.1200925926</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>46290.12333333334</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>46290.12922453704</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>46290.13246527778</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>46290.13570601852</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>46290.14158564815</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>46290.14482638889</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>46290.14806712963</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>46290.15395833334</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>46290.15719907408</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>46290.16043981481</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>46290.16633101852</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>46290.16957175926</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>46290.1728125</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>46290.17870370371</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>46290.18194444444</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>46290.18518518518</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>46290.19107638889</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>46290.19431712963</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="n">
+        <v>46290.19755787037</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="n">
+        <v>46290.2034375</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>46290.20668981481</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>46290.20993055555</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
+        <v>46290.21582175926</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>46290.2190625</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>46290.22230324074</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>46290.22818287037</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>46290.23143518518</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>46290.23467592592</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>46290.24056712963</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>46290.24380787037</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>46290.24704861111</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>46290.25293981482</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>46290.25618055555</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>46290.25942129629</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>46290.2653125</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>46290.26856481482</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>46290.27180555555</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>46290.27769675926</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>46290.2809375</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>46290.28417824074</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>46290.29006944445</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>46290.29331018519</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>46290.2965625</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>46290.30245370371</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>46290.30569444445</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>46290.30893518519</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>46290.31482638889</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="n">
+        <v>46290.31806712963</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="n">
+        <v>46290.32130787037</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="n">
+        <v>46290.32719907408</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="n">
+        <v>46290.33043981482</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>46290.33368055556</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>46290.33957175926</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>46290.3428125</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>46290.34606481482</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>46290.35194444445</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>46290.35518518519</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>46290.35842592592</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>46290.36431712963</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>46290.36754629629</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>46290.37079861111</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>46290.37667824074</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>46290.37993055556</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>46290.38315972222</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>46290.3890625</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>46290.39230324074</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>46290.39554398148</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>46290.40143518519</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>46290.40467592593</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>46290.40792824074</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>46290.41380787037</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>46290.41706018519</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>46290.42030092593</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>46290.42622685185</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46290.42946759259</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>46290.43270833333</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="n">
+        <v>46290.43863425926</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="n">
+        <v>46290.441875</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="n">
+        <v>46290.44511574074</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="n">
+        <v>46290.45104166667</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="n">
+        <v>46290.45429398148</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="n">
+        <v>46290.45753472222</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>46290.46342592593</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>46290.46991898148</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>46290.47579861111</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>46290.47903935185</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>46290.48229166667</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>46290.4881712963</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>46290.49142361111</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>46290.49466435185</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>46290.50055555555</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>46290.50380787037</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>46290.50703703704</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>46290.51292824074</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>46290.51618055555</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>46290.51943287037</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>46290.5253125</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>46290.52855324074</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>46290.53179398148</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>46290.53768518518</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>46290.5409375</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>46290.54417824074</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo autenticar como Administrador en la ONU (todas las credenciales fueron rechazadas). Para restaurar las credenciales de fábrica (admin / stdONU101); por favor mantén presionado el botón físico de RESET en la ONU durante 10 a 15 segundos con el equipo encendido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>46290.54903935185</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>YA_CONFIGURADA</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>ONU ya posee VLAN 3 activa y firmware configurado</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>46290.55633101852</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo ingresar con credenciales finales (Powerlink)</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>46290.56597222222</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>YA_CONFIGURADA</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>ONU ya estaba en estado final con VLAN3 verificada</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="n">
+        <v>46290.5678125</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:6A:7E</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>VSOL00BA6A7E</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>YA_CONFIGURADA</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>ONU ya estaba en estado final con VLAN3 verificada</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="n">
+        <v>46290.60460648148</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Fallo: La ONU reporto fallo en la actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="n">
+        <v>46290.60869212963</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Fallo: La ONU reporto fallo en la actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>46290.61832175926</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Fallo: La ONU reporto fallo en la actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>46290.62340277778</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Fallo: No se pudo ingresar con credenciales finales (Powerlink)</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>46290.63846064815</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Fallo: La ONU reporto fallo en la actualizacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>46290.6444675926</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Firmware cargado y reset OK, pero VLAN3 NO encontrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>46290.64969907407</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>4C:46:D1:BA:48:FA</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>VSOL00BA48FA</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>YA_CONFIGURADA</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>ONU ya estaba en estado final con VLAN3 verificada</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>46290.66555555556</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>10.100.1.1</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr"/>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Fallo: ONU no se estabilizo (auto-reinicio pendiente)</t>
         </is>
       </c>
     </row>
